--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.56129091314295</v>
+        <v>6.103709773385729</v>
       </c>
       <c r="D2" t="n">
-        <v>31.80071286296946</v>
+        <v>5.167615840232537</v>
       </c>
       <c r="E2" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F2" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.73145081104929</v>
+        <v>5.806360756795509</v>
       </c>
       <c r="D3" t="n">
-        <v>11.31732550447084</v>
+        <v>1.839065394476512</v>
       </c>
       <c r="E3" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F3" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.98345748207477</v>
+        <v>4.709811840837149</v>
       </c>
       <c r="D4" t="n">
-        <v>28.80354352951538</v>
+        <v>4.680575823546249</v>
       </c>
       <c r="E4" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F4" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.86630951203684</v>
+        <v>3.228275295705986</v>
       </c>
       <c r="D5" t="n">
-        <v>8.657255564214218</v>
+        <v>1.406804029184811</v>
       </c>
       <c r="E5" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F5" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.078855100990888</v>
+        <v>0.9878139539110192</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5591756360639</v>
+        <v>5.615866040860384</v>
       </c>
       <c r="E6" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F6" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.31142156742831</v>
+        <v>3.300606004707101</v>
       </c>
       <c r="D7" t="n">
-        <v>18.70024002462282</v>
+        <v>3.038789004001209</v>
       </c>
       <c r="E7" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F7" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.59255754389865</v>
+        <v>4.808790600883531</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6830082794472</v>
+        <v>4.82348884541017</v>
       </c>
       <c r="E8" t="n">
-        <v>10.10559575372126</v>
+        <v>1.642159309979705</v>
       </c>
       <c r="F8" t="n">
-        <v>9.630233895485556</v>
+        <v>1.564913008016403</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
